--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:49:03+00:00</t>
+    <t>2024-01-29T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:55:21+00:00</t>
+    <t>2024-01-29T12:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -642,14 +642,14 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-nationality}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality}
 </t>
   </si>
   <si>
-    <t>FR Core Patient Nationalité</t>
-  </si>
-  <si>
-    <t>Nationalité du patient</t>
+    <t>Nationality</t>
+  </si>
+  <si>
+    <t>The nationality of the patient.</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5005" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="680">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:33:53+00:00</t>
+    <t>2024-01-29T12:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -800,7 +800,7 @@
 </t>
   </si>
   <si>
-    <t>National Health Identifier | Identifiant national de santé</t>
+    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS validée, il est nécessaire de respecter la conformité au profil FrCorePatientINS. Les identifiants NIR et NIA ne sont définis uniquement dans le cas du FRCorePatientINS.</t>
   </si>
   <si>
     <t>An identifier for this patient.</t>
@@ -1661,10 +1661,7 @@
     <t>Most, if not all systems capture it.</t>
   </si>
   <si>
-    <t>The domestic partnership status of a person.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -4755,7 +4752,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -7922,7 +7919,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -10038,7 +10035,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -14452,11 +14449,9 @@
       <c r="X102" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y102" t="s" s="2">
+      <c r="Y102" s="2"/>
+      <c r="Z102" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14489,16 +14484,16 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AL102" t="s" s="2">
+      <c r="AM102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14506,10 +14501,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14532,19 +14527,19 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14593,7 +14588,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14608,7 +14603,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>109</v>
@@ -14617,7 +14612,7 @@
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14625,10 +14620,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14651,19 +14646,19 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14712,7 +14707,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14724,10 +14719,10 @@
         <v>101</v>
       </c>
       <c r="AJ104" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AK104" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>109</v>
@@ -14736,7 +14731,7 @@
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -14744,10 +14739,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14770,19 +14765,19 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14831,7 +14826,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14843,10 +14838,10 @@
         <v>101</v>
       </c>
       <c r="AJ105" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AK105" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>109</v>
@@ -14863,10 +14858,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14978,10 +14973,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15095,13 +15090,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>81</v>
@@ -15123,13 +15118,13 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15212,13 +15207,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>81</v>
@@ -15240,13 +15235,13 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15329,14 +15324,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15358,10 +15353,10 @@
         <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>115</v>
@@ -15416,7 +15411,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15448,10 +15443,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15477,16 +15472,16 @@
         <v>273</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>521</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15514,16 +15509,16 @@
         <v>153</v>
       </c>
       <c r="Y111" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Z111" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="Z111" t="s" s="2">
+      <c r="AA111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB111" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AC111" s="2"/>
       <c r="AD111" t="s" s="2">
@@ -15533,7 +15528,7 @@
         <v>118</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15548,7 +15543,7 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>109</v>
@@ -15557,7 +15552,7 @@
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15565,13 +15560,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C112" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>81</v>
@@ -15596,16 +15591,16 @@
         <v>273</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>521</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15634,7 +15629,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15652,7 +15647,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15667,7 +15662,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>109</v>
@@ -15676,7 +15671,7 @@
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>81</v>
@@ -15684,13 +15679,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C113" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>81</v>
@@ -15715,16 +15710,16 @@
         <v>273</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>521</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15753,7 +15748,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -15771,7 +15766,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15786,7 +15781,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>109</v>
@@ -15795,7 +15790,7 @@
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>81</v>
@@ -15803,10 +15798,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15832,16 +15827,16 @@
         <v>382</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15890,7 +15885,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15905,16 +15900,16 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>81</v>
@@ -15922,10 +15917,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15957,7 +15952,7 @@
         <v>483</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="O115" t="s" s="2">
         <v>485</v>
@@ -16009,7 +16004,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16041,10 +16036,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16067,19 +16062,19 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>240</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
@@ -16128,7 +16123,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16143,7 +16138,7 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>109</v>
@@ -16152,7 +16147,7 @@
         <v>81</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>81</v>
@@ -16160,10 +16155,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16192,13 +16187,13 @@
         <v>490</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>442</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
@@ -16247,7 +16242,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16271,7 +16266,7 @@
         <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>81</v>
@@ -16279,10 +16274,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16308,16 +16303,16 @@
         <v>308</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>81</v>
@@ -16366,7 +16361,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16375,13 +16370,13 @@
         <v>89</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>313</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>109</v>
@@ -16390,7 +16385,7 @@
         <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>81</v>
@@ -16398,10 +16393,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16427,10 +16422,10 @@
         <v>299</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>302</v>
@@ -16483,7 +16478,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16498,7 +16493,7 @@
         <v>304</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>109</v>
@@ -16507,7 +16502,7 @@
         <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>81</v>
@@ -16515,10 +16510,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16541,19 +16536,19 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16602,7 +16597,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16617,10 +16612,10 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AL120" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
@@ -16634,10 +16629,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16749,10 +16744,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16866,14 +16861,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16895,10 +16890,10 @@
         <v>112</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>115</v>
@@ -16953,7 +16948,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16985,10 +16980,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17014,16 +17009,16 @@
         <v>273</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17072,7 +17067,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>89</v>
@@ -17087,16 +17082,16 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AL124" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AL124" t="s" s="2">
+      <c r="AM124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>81</v>
@@ -17104,10 +17099,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17133,16 +17128,16 @@
         <v>373</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17191,7 +17186,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17206,16 +17201,16 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="AL125" t="s" s="2">
+      <c r="AM125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17223,14 +17218,14 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17249,16 +17244,16 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17308,7 +17303,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17323,7 +17318,7 @@
         <v>313</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>109</v>
@@ -17332,7 +17327,7 @@
         <v>81</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>81</v>
@@ -17340,10 +17335,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17366,19 +17361,19 @@
         <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -17427,7 +17422,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17442,10 +17437,10 @@
         <v>313</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>81</v>
@@ -17459,10 +17454,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17485,19 +17480,19 @@
         <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
@@ -17546,7 +17541,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17561,7 +17556,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>109</v>
@@ -17578,10 +17573,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17693,10 +17688,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17810,14 +17805,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17839,10 +17834,10 @@
         <v>112</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>115</v>
@@ -17897,7 +17892,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17929,10 +17924,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17955,16 +17950,16 @@
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18014,7 +18009,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>89</v>
@@ -18038,7 +18033,7 @@
         <v>81</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18046,10 +18041,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18075,10 +18070,10 @@
         <v>173</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>442</v>
@@ -18110,11 +18105,11 @@
         <v>267</v>
       </c>
       <c r="Y133" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="Z133" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="Z133" t="s" s="2">
-        <v>679</v>
-      </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18131,7 +18126,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>89</v>
@@ -18146,7 +18141,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>109</v>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:36:14+00:00</t>
+    <t>2024-01-29T12:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
